--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תאיר מרציאנו - מחרוזת קיץ 2026</v>
+        <v>שלומי ימין - רוקדת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410768&amp;sid=32c601c210b460583a1c8e7094286233</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410793&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תאיר מרציאנו - מחרוזת קיץ 2026</v>
+        <v>שלומי ימין - רוקדת</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שניר כהן - מה קורה לי</v>
+        <v>שלומי ימין - הגבר של חיי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410767&amp;sid=32c601c210b460583a1c8e7094286233</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410792&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שניר כהן - מה קורה לי</v>
+        <v>שלומי ימין - הגבר של חיי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שימי תבורי - את כלה</v>
+        <v>שלומי ימין - בַּלֵּילוֹת כְּשֶׁהָעוֹלָם סוֹעֵר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410766&amp;sid=32c601c210b460583a1c8e7094286233</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410791&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שימי תבורי - את כלה</v>
+        <v>שלומי ימין - בַּלֵּילוֹת כְּשֶׁהָעוֹלָם סוֹעֵר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שי בסיל - נשף מסכות</v>
+        <v>שירז אברהם - אבא תודה - גרסה אקוסטית</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410765&amp;sid=32c601c210b460583a1c8e7094286233</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410790&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,12 +583,430 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שי בסיל - נשף מסכות</v>
+        <v>שירז אברהם - אבא תודה - גרסה אקוסטית</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>רגב הוד - מחרוזת יותר מידי שנים 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410789&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>רגב הוד - מחרוזת יותר מידי שנים 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>עדי עייש - דופק אותי הגעגוע</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410788&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>עדי עייש - דופק אותי הגעגוע</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ניב אבוטבול - הפרויקט של הדיכאון של ניב 2 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410787&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ניב אבוטבול - הפרויקט של הדיכאון של ניב 2 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מושיקו מור - אלינור</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410786&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מושיקו מור - אלינור</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ירין פרחן - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410785&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ירין פרחן - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>זכי צברי - מחרוזת לֵגֶה אוֹטִי תֵ'ס לֵגֶה 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410784&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>זכי צברי - מחרוזת לֵגֶה אוֹטִי תֵ'ס לֵגֶה 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>הדר אבני &amp; דקלה תפילין - שם טבעת</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410783&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>הדר אבני &amp; דקלה תפילין - שם טבעת</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דנה עדיני - אהבה טהורה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410782&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דנה עדיני - אהבה טהורה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אלסי דול - 00:00 (אמאלה)</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410781&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אלסי דול - 00:00 (אמאלה)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אור משה - אבא</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410780&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אור משה - אבא</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אבי חן - Toy Muborak</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410779&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אבי חן - Toy Muborak</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי ימין - רוקדת</v>
+        <v>שמואל - שיר אהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410793&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410806&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי ימין - רוקדת</v>
+        <v>שמואל - שיר אהבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלומי ימין - הגבר של חיי</v>
+        <v>קרולינה &amp; אורי בראונר כנרות - תפילה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410792&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410805&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלומי ימין - הגבר של חיי</v>
+        <v>קרולינה &amp; אורי בראונר כנרות - תפילה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שלומי ימין - בַּלֵּילוֹת כְּשֶׁהָעוֹלָם סוֹעֵר</v>
+        <v>קארין שוקרי - זאת שמרצה</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410791&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410804&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שלומי ימין - בַּלֵּילוֹת כְּשֶׁהָעוֹלָם סוֹעֵר</v>
+        <v>קארין שוקרי - זאת שמרצה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שירז אברהם - אבא תודה - גרסה אקוסטית</v>
+        <v>עדן חסון - כל הברכה שלי</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410790&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410803&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שירז אברהם - אבא תודה - גרסה אקוסטית</v>
+        <v>עדן חסון - כל הברכה שלי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רגב הוד - מחרוזת יותר מידי שנים 2026</v>
+        <v>נועה קירל - הכי יפה כשטעים לך</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410789&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410802&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רגב הוד - מחרוזת יותר מידי שנים 2026</v>
+        <v>נועה קירל - הכי יפה כשטעים לך</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>עדי עייש - דופק אותי הגעגוע</v>
+        <v>ג'קו אייזנברג &amp; רון נשר - קיווינו</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410788&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410801&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>עדי עייש - דופק אותי הגעגוע</v>
+        <v>ג'קו אייזנברג &amp; רון נשר - קיווינו</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ניב אבוטבול - הפרויקט של הדיכאון של ניב 2 2026</v>
+        <v>גוסטו - אל תלכי לי מאמי לאיבוד</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410787&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410800&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ניב אבוטבול - הפרויקט של הדיכאון של ניב 2 2026</v>
+        <v>גוסטו - אל תלכי לי מאמי לאיבוד</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>מושיקו מור - אלינור</v>
+        <v>בן גדסי - נסיכה בלי נסיכים</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410786&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410799&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>מושיקו מור - אלינור</v>
+        <v>בן גדסי - נסיכה בלי נסיכים</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ירין פרחן - עיניים עצובות קאבר</v>
+        <v>אריאל רייכל - אדון עולם</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410785&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410798&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ירין פרחן - עיניים עצובות קאבר</v>
+        <v>אריאל רייכל - אדון עולם</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>זכי צברי - מחרוזת לֵגֶה אוֹטִי תֵ'ס לֵגֶה 2026</v>
+        <v>אסף הרוש - להרים עיניים</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410784&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410797&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>זכי צברי - מחרוזת לֵגֶה אוֹטִי תֵ'ס לֵגֶה 2026</v>
+        <v>אסף הרוש - להרים עיניים</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>הדר אבני &amp; דקלה תפילין - שם טבעת</v>
+        <v>אליה והב - ירושלים</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410783&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410796&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>הדר אבני &amp; דקלה תפילין - שם טבעת</v>
+        <v>אליה והב - ירושלים</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>דנה עדיני - אהבה טהורה</v>
+        <v>אור בר - מתוק או מר</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410782&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410795&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>דנה עדיני - אהבה טהורה</v>
+        <v>אור בר - מתוק או מר</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אלסי דול - 00:00 (אמאלה)</v>
+        <v>אופיר כלב - כאן איתי</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410781&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410794&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -925,88 +925,12 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>אלסי דול - 00:00 (אמאלה)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אור משה - אבא</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-09</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410780&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-09</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אור משה - אבא</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אבי חן - Toy Muborak</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-05-09</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410779&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-05-09</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אבי חן - Toy Muborak</v>
+        <v>אופיר כלב - כאן איתי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמואל - שיר אהבה</v>
+        <v>קלניא - מחרוזת ציפור זרה 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410806&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410817&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמואל - שיר אהבה</v>
+        <v>קלניא - מחרוזת ציפור זרה 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קרולינה &amp; אורי בראונר כנרות - תפילה</v>
+        <v>קלניא - עד יום מותי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410805&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410816&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קרולינה &amp; אורי בראונר כנרות - תפילה</v>
+        <v>קלניא - עד יום מותי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קארין שוקרי - זאת שמרצה</v>
+        <v>פרחי ירושלים - ירושלים</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410804&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410815&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קארין שוקרי - זאת שמרצה</v>
+        <v>פרחי ירושלים - ירושלים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עדן חסון - כל הברכה שלי</v>
+        <v>עומר צמח - לב מדבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410803&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410814&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עדן חסון - כל הברכה שלי</v>
+        <v>עומר צמח - לב מדבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נועה קירל - הכי יפה כשטעים לך</v>
+        <v>מיה כהן - כביסה מלוכלכת</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410802&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410813&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נועה קירל - הכי יפה כשטעים לך</v>
+        <v>מיה כהן - כביסה מלוכלכת</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ג'קו אייזנברג &amp; רון נשר - קיווינו</v>
+        <v>זנטי - זזה</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410801&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410812&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ג'קו אייזנברג &amp; רון נשר - קיווינו</v>
+        <v>זנטי - זזה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>גוסטו - אל תלכי לי מאמי לאיבוד</v>
+        <v>זואי דגן - משמעות אחרת</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410800&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410811&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>גוסטו - אל תלכי לי מאמי לאיבוד</v>
+        <v>זואי דגן - משמעות אחרת</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>בן גדסי - נסיכה בלי נסיכים</v>
+        <v>דודו טסה - אביב בחוץ</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410799&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410810&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>בן גדסי - נסיכה בלי נסיכים</v>
+        <v>דודו טסה - אביב בחוץ</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אריאל רייכל - אדון עולם</v>
+        <v>גיא זהבי &amp; אורי שוחט - משוך בחבל</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410798&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410809&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אריאל רייכל - אדון עולם</v>
+        <v>גיא זהבי &amp; אורי שוחט - משוך בחבל</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אסף הרוש - להרים עיניים</v>
+        <v>אסתר גד - תלוי ועומד</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410797&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410808&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,126 +811,12 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אסף הרוש - להרים עיניים</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אליה והב - ירושלים</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410796&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אליה והב - ירושלים</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אור בר - מתוק או מר</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410795&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אור בר - מתוק או מר</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אופיר כלב - כאן איתי</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410794&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אופיר כלב - כאן איתי</v>
+        <v>אסתר גד - תלוי ועומד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קלניא - מחרוזת ציפור זרה 2026</v>
+        <v>אופיר סלומון - מה נהיה ממני</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410817&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410819&amp;sid=678301c7d441635eca10ba6cfbe7b50e</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קלניא - מחרוזת ציפור זרה 2026</v>
+        <v>אופיר סלומון - מה נהיה ממני</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קלניא - עד יום מותי</v>
+        <v>אודי דמארי - ניגון שלווה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410816&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410818&amp;sid=678301c7d441635eca10ba6cfbe7b50e</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,316 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קלניא - עד יום מותי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>פרחי ירושלים - ירושלים</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410815&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>פרחי ירושלים - ירושלים</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עומר צמח - לב מדבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410814&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עומר צמח - לב מדבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מיה כהן - כביסה מלוכלכת</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410813&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מיה כהן - כביסה מלוכלכת</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>זנטי - זזה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410812&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>זנטי - זזה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>זואי דגן - משמעות אחרת</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410811&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>זואי דגן - משמעות אחרת</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>דודו טסה - אביב בחוץ</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410810&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>דודו טסה - אביב בחוץ</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>גיא זהבי &amp; אורי שוחט - משוך בחבל</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410809&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>גיא זהבי &amp; אורי שוחט - משוך בחבל</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אסתר גד - תלוי ועומד</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410808&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אסתר גד - תלוי ועומד</v>
+        <v>אודי דמארי - ניגון שלווה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר סלומון - מה נהיה ממני</v>
+        <v>עמית אשכנזי - אין לך מקום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410819&amp;sid=678301c7d441635eca10ba6cfbe7b50e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410836&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-12</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר סלומון - מה נהיה ממני</v>
+        <v>עמית אשכנזי - אין לך מקום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אודי דמארי - ניגון שלווה</v>
+        <v>עומר דוד - מהמזרח לתל אביב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410818&amp;sid=678301c7d441635eca10ba6cfbe7b50e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410835&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-12</v>
@@ -507,12 +507,582 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אודי דמארי - ניגון שלווה</v>
+        <v>עומר דוד - מהמזרח לתל אביב</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נהוראי רחמימוב - איתי כאן לעד</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410834&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נהוראי רחמימוב - איתי כאן לעד</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מן יהל - נשבר לי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410833&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מן יהל - נשבר לי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ישראל בן חמו - בר יוחאי יסוד עולם</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410832&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ישראל בן חמו - בר יוחאי יסוד עולם</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>שחר טבוך &amp; מאיה דדון - הנסיך של רמת גן</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410831&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>שחר טבוך &amp; מאיה דדון - הנסיך של רמת גן</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מתי שריקי - מזמור לתודה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410830&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מתי שריקי - מזמור לתודה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מאי טוויק - שישרפו הקנאים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410829&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מאי טוויק - שישרפו הקנאים</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>יעקב הראל - מחרוזת אבא תודה 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410828&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>יעקב הראל - מחרוזת אבא תודה 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יוחנן - שלום</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410827&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יוחנן - שלום</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>חביב חיים בן אריה - אל מול הים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410826&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>חביב חיים בן אריה - אל מול הים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דניאל בוחבוט - מחרוזת חצי לב 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410825&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דניאל בוחבוט - מחרוזת חצי לב 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>בן ימין - פריק של טעויות</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410824&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>בן ימין - פריק של טעויות</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אלעד אלדד &amp; ינון דודיאן - אני אוהב אותך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410823&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אלעד אלדד &amp; ינון דודיאן - אני אוהב אותך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אליה ביטון - מכאן זה לנצח</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410822&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אליה ביטון - מכאן זה לנצח</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>איתי בירמן &amp; אריאל זילבר - אשריכם</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410821&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>איתי בירמן &amp; אריאל זילבר - אשריכם</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אילאי ברדה - חזק אני</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410820&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אילאי ברדה - חזק אני</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמית אשכנזי - אין לך מקום</v>
+        <v>שר-אל - מנגינות של כאב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410836&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410841&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-12</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמית אשכנזי - אין לך מקום</v>
+        <v>שר-אל - מנגינות של כאב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עומר דוד - מהמזרח לתל אביב</v>
+        <v>שניר עזרן - אם רק תחזרי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410835&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410840&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-12</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עומר דוד - מהמזרח לתל אביב</v>
+        <v>שניר עזרן - אם רק תחזרי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נהוראי רחמימוב - איתי כאן לעד</v>
+        <v>שלומי ימין - אין על מה לחשוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410834&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410839&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-12</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נהוראי רחמימוב - איתי כאן לעד</v>
+        <v>שלומי ימין - אין על מה לחשוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מן יהל - נשבר לי</v>
+        <v>שי וינר - כנפי השכינה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410833&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410838&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-12</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מן יהל - נשבר לי</v>
+        <v>שי וינר - כנפי השכינה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ישראל בן חמו - בר יוחאי יסוד עולם</v>
+        <v>עמית סמוכי - קצת נשימה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410832&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410837&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-12</v>
@@ -621,468 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ישראל בן חמו - בר יוחאי יסוד עולם</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>שחר טבוך &amp; מאיה דדון - הנסיך של רמת גן</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410831&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>שחר טבוך &amp; מאיה דדון - הנסיך של רמת גן</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>מתי שריקי - מזמור לתודה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410830&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>מתי שריקי - מזמור לתודה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>מאי טוויק - שישרפו הקנאים</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410829&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>מאי טוויק - שישרפו הקנאים</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>יעקב הראל - מחרוזת אבא תודה 2026</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410828&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>יעקב הראל - מחרוזת אבא תודה 2026</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>יוחנן - שלום</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410827&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>יוחנן - שלום</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>חביב חיים בן אריה - אל מול הים</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410826&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>חביב חיים בן אריה - אל מול הים</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>דניאל בוחבוט - מחרוזת חצי לב 2026</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410825&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>דניאל בוחבוט - מחרוזת חצי לב 2026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>בן ימין - פריק של טעויות</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410824&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>בן ימין - פריק של טעויות</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אלעד אלדד &amp; ינון דודיאן - אני אוהב אותך</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410823&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אלעד אלדד &amp; ינון דודיאן - אני אוהב אותך</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אליה ביטון - מכאן זה לנצח</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410822&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אליה ביטון - מכאן זה לנצח</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>איתי בירמן &amp; אריאל זילבר - אשריכם</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410821&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>איתי בירמן &amp; אריאל זילבר - אשריכם</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>אילאי ברדה - חזק אני</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410820&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v>אילאי ברדה - חזק אני</v>
+        <v>עמית סמוכי - קצת נשימה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שר-אל - מנגינות של כאב</v>
+        <v>ליעד אלון - כולי תפילה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410841&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410873&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שר-אל - מנגינות של כאב</v>
+        <v>ליעד אלון - כולי תפילה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שניר עזרן - אם רק תחזרי</v>
+        <v>לינור דהן - דור צמא</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410840&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410872&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שניר עזרן - אם רק תחזרי</v>
+        <v>לינור דהן - דור צמא</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שלומי ימין - אין על מה לחשוב</v>
+        <v>ירין נקטלוב - תכף הענן יחלוף</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410839&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410871&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שלומי ימין - אין על מה לחשוב</v>
+        <v>ירין נקטלוב - תכף הענן יחלוף</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שי וינר - כנפי השכינה</v>
+        <v>חיים יהודה מארח את דוד יהודה - אורך כבר יאיר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410838&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410870&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שי וינר - כנפי השכינה</v>
+        <v>חיים יהודה מארח את דוד יהודה - אורך כבר יאיר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עמית סמוכי - קצת נשימה</v>
+        <v>זואי דגן - גשרים</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410837&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410869&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,12 +621,126 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עמית סמוכי - קצת נשימה</v>
+        <v>זואי דגן - גשרים</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>דניאל אזולאי - מחרוזת חשמל באויר 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410868&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>דניאל אזולאי - מחרוזת חשמל באויר 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דוד ברג - זה לטובה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410867&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דוד ברג - זה לטובה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אורי זר - תמיד בלב אמא</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410866&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אורי זר - תמיד בלב אמא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליעד אלון - כולי תפילה</v>
+        <v>יהודה בורן &amp; נתנאל אמסילי - ירושלים קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410873&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410880&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-14</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליעד אלון - כולי תפילה</v>
+        <v>יהודה בורן &amp; נתנאל אמסילי - ירושלים קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>לינור דהן - דור צמא</v>
+        <v>אלינור מנו - מנגינה שקטה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410872&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410879&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-14</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>לינור דהן - דור צמא</v>
+        <v>אלינור מנו - מנגינה שקטה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ירין נקטלוב - תכף הענן יחלוף</v>
+        <v>תמר ריילי - אמן אמן אמן</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410871&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410878&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-14</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ירין נקטלוב - תכף הענן יחלוף</v>
+        <v>תמר ריילי - אמן אמן אמן</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>חיים יהודה מארח את דוד יהודה - אורך כבר יאיר</v>
+        <v>צדי אור - שיק תימני</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410870&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410877&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-14</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>חיים יהודה מארח את דוד יהודה - אורך כבר יאיר</v>
+        <v>צדי אור - שיק תימני</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>זואי דגן - גשרים</v>
+        <v>עילי בוטנר והילדים החדשים - גם בנים בוכים</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410869&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410876&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-14</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>זואי דגן - גשרים</v>
+        <v>עילי בוטנר והילדים החדשים - גם בנים בוכים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דניאל אזולאי - מחרוזת חשמל באויר 2026</v>
+        <v>נתנאל ברדה - אחד שלא עוזב (ירושלים)</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410868&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410875&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-14</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דניאל אזולאי - מחרוזת חשמל באויר 2026</v>
+        <v>נתנאל ברדה - אחד שלא עוזב (ירושלים)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דוד ברג - זה לטובה</v>
+        <v>מוטי אוריאל - ירושלים</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410867&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410874&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-14</v>
@@ -697,50 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>דוד ברג - זה לטובה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אורי זר - תמיד בלב אמא</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410866&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אורי זר - תמיד בלב אמא</v>
+        <v>מוטי אוריאל - ירושלים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>